--- a/consent_forms/046_hair_toner_mix_application_consent_form--consent_forms.xlsx
+++ b/consent_forms/046_hair_toner_mix_application_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -692,8 +692,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -721,12 +721,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'text':_'i_am_18_years_old_or_older'}</t>
+          <t>i_am_18_years_old_or_older</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'text': 'I am 18 years old or older'}</t>
+          <t>I am 18 years old or older</t>
         </is>
       </c>
     </row>
@@ -738,12 +738,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'text':_'i_am_under_18_years_old'}</t>
+          <t>i_am_under_18_years_old</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'text': 'I am under 18 years old'}</t>
+          <t>I am under 18 years old</t>
         </is>
       </c>
     </row>
@@ -755,12 +755,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'text':_'cut'}</t>
+          <t>cut</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'text': 'Cut'}</t>
+          <t>Cut</t>
         </is>
       </c>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'text':_'color'}</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'text': 'Color'}</t>
+          <t>Color</t>
         </is>
       </c>
     </row>
@@ -789,12 +789,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'text':_'chemical_treatment'}</t>
+          <t>chemical_treatment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'text': 'Chemical treatment'}</t>
+          <t>Chemical treatment</t>
         </is>
       </c>
     </row>
